--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112077361</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118203749</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118203750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126425188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69739717</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127895031</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69661495</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2539432</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69661429</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126425192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3001517</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69661424</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2114,6 +2179,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69661489</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2216,6 +2286,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69739560</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2318,6 +2393,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69739561</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2420,6 +2500,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69739605</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112077376</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118203756</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2756,8 +2851,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126425207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2854,6 +2854,123 @@
       <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126425207</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136151572</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora Mälaren, Rö, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>691570</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6623773</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136151572</t>
         </is>
       </c>
     </row>
@@ -2878,6 +2995,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99281</v>
+        <v>99287</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99287</v>
+        <v>99288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99288</v>
+        <v>99299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99299</v>
+        <v>99312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99312</v>
+        <v>99313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99313</v>
+        <v>99326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
